--- a/temp/BBVA_VISA_20250626.xlsx
+++ b/temp/BBVA_VISA_20250626.xlsx
@@ -471,12 +471,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>-955090.66</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-955090,66</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -496,12 +498,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>-11.43</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-11,43</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -521,12 +525,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>12000</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>12000,0</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -546,12 +552,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>54104.01</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>54104,01</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -571,12 +579,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>35580</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>35580,0</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -596,12 +606,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>10800</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>10800,0</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -621,12 +633,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>79600</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>79600,0</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -646,12 +660,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>4300</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4300,0</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -671,12 +687,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>3400</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3400,0</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -696,12 +714,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>36609.3</v>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>36609,3</t>
+        </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -721,12 +741,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>20900</v>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>20900,0</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -746,12 +768,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>15700</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>15700,0</t>
+        </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -771,12 +795,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>4546.95</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4546,95</t>
+        </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -796,12 +822,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>28200</v>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>28200,0</t>
+        </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -821,12 +849,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>20520</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>20520,0</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -846,12 +876,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>264400</v>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>264400,0</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -871,12 +903,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>34515</v>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>34515,0</t>
+        </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -896,12 +930,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>950</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>950,0</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -921,12 +957,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>3722.79</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3722,79</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -946,12 +984,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>12026.95</v>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>12026,95</t>
+        </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -971,12 +1011,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>2068.84</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2068,84</t>
+        </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -996,12 +1038,14 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D23" t="n">
-        <v>8.23</v>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>8,23</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1065,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D24" t="n">
-        <v>15740.56</v>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>15740,56</t>
+        </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1092,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>44251</v>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>44251,0</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1119,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>8494.940000000001</v>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8494,94</t>
+        </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1146,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D27" t="n">
-        <v>11930.81</v>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>11930,81</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BBVA VISA</t>
+          <t>BBVA Visa</t>
         </is>
       </c>
     </row>

--- a/temp/BBVA_VISA_20250626.xlsx
+++ b/temp/BBVA_VISA_20250626.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PERSONAL FLOW    300060254971003</t>
+          <t>PERSONAL FLOW 300060254971003</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MERPAGO*HAVANNAFOODLI</t>
+          <t>MERPAGO*PUMA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4300,0</t>
+          <t>36609,3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ESTAC DISTRICTO ARCOS</t>
+          <t>MERPAGO*HAVANNAFOODLI</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3400,0</t>
+          <t>4300,0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MERPAGO*PUMA</t>
+          <t>MERPAGO*WENDYS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>36609,3</t>
+          <t>20900,0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MERPAGO*WENDYS</t>
+          <t>ESTAC DISTRICTO ARCOS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20900,0</t>
+          <t>3400,0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>METROGAS SA DEB  040000136346</t>
+          <t>MERPAGO*RINCONNORTENO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4546,95</t>
+          <t>28200,0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MERPAGO*RINCONNORTENO</t>
+          <t>METROGAS SA DEB 040000136346</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>28200,0</t>
+          <t>4546,95</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PEDIDOSYA</t>
+          <t>EDENOR SA 000007691385963</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>34515,0</t>
+          <t>12026,95</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PEDIDOSYA*PROPINA</t>
+          <t>AUBASA 960001911719401</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>950,0</t>
+          <t>3722,79</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AUBASA           960001911719401</t>
+          <t>PEDIDOSYA*PROPINA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3722,79</t>
+          <t>950,0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EDENOR SA        000007691385963</t>
+          <t>PEDIDOSYA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12026,95</t>
+          <t>34515,0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NETFLIX.COM      iEQbXskdg97PI0sM</t>
+          <t>NETFLIX.COM iEQbXskdg USD 8,23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BBVA SEGUROS A2052000420510-023-0</t>
+          <t>BBVA SEGUROS A2052000420510-023-000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1152,6 +1152,654 @@
         </is>
       </c>
       <c r="E27" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PAYU*AR*UBER</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>4690,0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TRIUNFO COOP D0000007681097-094-009</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>48632,0</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>AUTOPISTAS URBAN 000000004488335</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>856,31</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MERPAGO*VEAEXPRESS</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1418,79</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MERPAGO*SUPERDIA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3980,0</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PEDIDOSYA _ PLUS</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1996,0</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MERPAGO*MIGUSTO</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>129105,0</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MERPAGO*CENTRALPAN</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>26520,0</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-07-19</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Spotify USD 2,60</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2,6</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MERPAGO*MCDONALDSECOMMERC</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>29000,0</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MERPAGO*FARMACITY</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>5200,0</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-07-20</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MERPAGO*MCDONALDS</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2000,0</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>EXPERTA SEGURO0000039091403-015-000</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>14787,37</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MERPAGO*ESCUELADAVINCI</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>306000,0</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SIRO -ROI SA 079001</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>83671,04</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PERSONAL FLOW 300060254971003</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>55712,02</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CABIFY2530IVLK9NRK</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>4311,0</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>001434K BONIF. CONSUMO CABIFY2530IVLK9NRK</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>-1077,75</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MERPAGO*SUPERDIA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>29137,5</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2025-07-27</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CINEMARK PALERMO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>35925,0</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SANDRULI SRL</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>11700,0</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>IIBB PERCEP-CABA 2,00%( 14241,45)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>284,82</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>IVA RG 4240 21%( 14241,45)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2990,7</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>BBVA Visa</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>DB.RG 5617 30% ( 14241,45 )</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ARS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>4272,43</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
         <is>
           <t>BBVA Visa</t>
         </is>
